--- a/excel_files/1.xlsx
+++ b/excel_files/1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,12 +449,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1-30</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>90-60</t>
+          <t>90-80</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -470,19 +470,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31-60</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>60-30</t>
+          <t>80-70</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -491,19 +491,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>61-90</t>
+          <t>21-30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30-0</t>
+          <t>70-60</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91-120</t>
+          <t>31-40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0-330</t>
+          <t>60-50</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -533,12 +533,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>121-150</t>
+          <t>41-50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>330-300</t>
+          <t>50-40</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -554,19 +554,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>151-180</t>
+          <t>51-60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>300-270</t>
+          <t>40-30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -575,19 +575,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>181-210</t>
+          <t>61-70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>270-240</t>
+          <t>30-20</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -596,19 +596,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>211-240</t>
+          <t>71-80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>240-210</t>
+          <t>20-10</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -617,19 +617,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>241-270</t>
+          <t>81-90</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>210-180</t>
+          <t>10-0</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -638,12 +638,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>271-300</t>
+          <t>91-100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>180-150</t>
+          <t>0-350</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -659,12 +659,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>301-330</t>
+          <t>101-110</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>150-120</t>
+          <t>350-340</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -680,18 +680,522 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>331-360</t>
+          <t>111-120</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>120-90</t>
+          <t>340-330</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>121-130</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>330-320</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>131-140</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>320-310</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>141-150</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>310-300</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>151-160</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>300-290</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>161-170</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>290-280</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>171-180</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>280-270</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>181-190</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>270-260</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>191-200</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>260-250</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>201-210</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>250-240</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>211-220</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>240-230</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>221-230</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>230-220</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>231-240</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>220-210</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>241-250</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>210-200</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>251-260</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>200-190</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>261-270</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>190-180</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>271-280</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>180-170</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>281-290</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>170-160</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>291-300</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>160-150</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301-310</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>150-140</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>311-320</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>140-130</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>321-330</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>130-120</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>331-340</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>120-110</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>341-350</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>110-100</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>351-360</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>100-90</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_files/1.xlsx
+++ b/excel_files/1.xlsx
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -881,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">

--- a/excel_files/1.xlsx
+++ b/excel_files/1.xlsx
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -902,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
